--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97451AA3-AEB3-8042-9F3C-E3D657EC2622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0BEE00-AAB3-2241-97AC-C7ECDA762E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25800" yWindow="760" windowWidth="25800" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="105">
   <si>
     <t>blank</t>
   </si>
@@ -113,9 +113,6 @@
     <t>Orthodoxie</t>
   </si>
   <si>
-    <t>Kunst</t>
-  </si>
-  <si>
     <t>Schriften</t>
   </si>
   <si>
@@ -200,9 +197,6 @@
     <t>yezidi.jpg</t>
   </si>
   <si>
-    <t>06_gegenseitiges.anerkennen.shahid.alam.png.webp</t>
-  </si>
-  <si>
     <t>synagogue-scroll.jpg</t>
   </si>
   <si>
@@ -287,9 +281,6 @@
     <t>Was macht einen Ort für Pilger "heilig"?</t>
   </si>
   <si>
-    <t>Die Gestaltung religiöser Kunst beobachten und beschreiben.</t>
-  </si>
-  <si>
     <t>ladenhaufReligiositaetUndSpiritualitaet2010</t>
   </si>
   <si>
@@ -305,9 +296,6 @@
     <t>Verständnis dafür zeigen, wie religiöse Identität, Gemeinschaft und Autorität in Online- und Offline-Umgebungen miteinander verwoben sind.</t>
   </si>
   <si>
-    <t>Kursbesuch: Kunst (Shahid Alam)</t>
-  </si>
-  <si>
     <t>Fundamentalismus, Radikalisierung und Extremismus definieren und Beispiele für jeden Begriff geben.</t>
   </si>
   <si>
@@ -318,6 +306,48 @@
   </si>
   <si>
     <t>Überlegen und erklären können, inwieweit religionswissenschaftliche Ansätze zum interreligiösen Dialog beitragen können, sollen und dürfen.</t>
+  </si>
+  <si>
+    <t>Religionswissenschaft</t>
+  </si>
+  <si>
+    <t>Was ist die Religionswissenschaft?</t>
+  </si>
+  <si>
+    <t>religionen-lupe.jpg</t>
+  </si>
+  <si>
+    <t>stausbergReligionswissenschaftWarumWas2025</t>
+  </si>
+  <si>
+    <t>Sich gegenseitig kennenlernen und unsere gegenseitige Ziele für den Kurs berücksichtigen.</t>
+  </si>
+  <si>
+    <t>Die Bestimmung des Fachs Religionswissenschaft in seiner Breite und mit seinen Unterschieden zur Theologie erfassen.</t>
+  </si>
+  <si>
+    <t>Was hat die Religionswissenschaft mit Kultur zu tun?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was sind 2 Ansätze, die Religion zu definieren? </t>
+  </si>
+  <si>
+    <t>Was haben Fußballrituale mit religiösen Ritualen gemeinsam?</t>
+  </si>
+  <si>
+    <t>slide-filename</t>
+  </si>
+  <si>
+    <t>slide-frontmatter</t>
+  </si>
+  <si>
+    <t>slide-body1</t>
+  </si>
+  <si>
+    <t>slide-body2</t>
+  </si>
+  <si>
+    <t>slide-content</t>
   </si>
 </sst>
 </file>
@@ -329,7 +359,7 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,13 +414,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -448,11 +471,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -759,7 +784,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -776,10 +801,10 @@
     <col min="13" max="13" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="77.83203125" customWidth="1"/>
     <col min="16" max="16" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5" customWidth="1"/>
+    <col min="17" max="22" width="44.33203125" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -823,16 +848,31 @@
         <v>11</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="14" t="s">
         <v>13</v>
       </c>
+      <c r="R1" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="S1" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="T1" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="U1" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="V1" s="14" t="s">
+        <v>104</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -850,7 +890,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" t="str">
@@ -862,18 +902,21 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>1-Vorstellung</v>
       </c>
+      <c r="N2" t="s">
+        <v>95</v>
+      </c>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P15" si="2">"["&amp;B2&amp;"]"</f>
         <v>[1]</v>
       </c>
-      <c r="Q2" t="str">
-        <f t="shared" ref="Q2:Q16" si="3">"---
+      <c r="Q2" s="15" t="str">
+        <f t="shared" ref="Q2" si="3">"---
 layout: post
 " &amp; B$1 &amp; ": " &amp; B2 &amp; "
 " &amp; P$1 &amp; ": " &amp; P2 &amp; "
@@ -886,8 +929,103 @@
 level: overview
 ---</v>
       </c>
+      <c r="R2" s="15" t="str">
+        <f>_xlfn.REGEXREPLACE(D2,"\.md","-slides.md")</f>
+        <v>2025-10-13-1-slides.md</v>
+      </c>
+      <c r="S2" s="15" t="str">
+        <f>"---
+layout: reveal
+title: '"&amp;G2&amp;"'
+author: 'Nathan Gibson'
+session: "&amp;B2&amp;"
+tags: ["&amp;B2&amp;",slides]
+category: slides
+image: "&amp;K2&amp;"
+parallaxBackgroundImage: 'assets/img/"&amp;K2&amp;"'
+---
+"</f>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Was machen wir hier?'
+author: 'Nathan Gibson'
+session: 1
+tags: [1,slides]
+category: slides
+image: candle.jpg
+parallaxBackgroundImage: 'assets/img/candle.jpg'
+---
+</v>
+      </c>
+      <c r="T2" s="15" t="str">
+        <f>"# Einführung in die Religionswissenschaft
+{: .r-fit-text}
+### "&amp;G2&amp;"
+Wintersemester 2025/2026
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+"&amp;N1&amp;"
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+"&amp;N2</f>
+        <v># Einführung in die Religionswissenschaft
+{: .r-fit-text}
+### Was machen wir hier?
+Wintersemester 2025/2026
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+objective
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Sich gegenseitig kennenlernen und unsere gegenseitige Ziele für den Kurs berücksichtigen.</v>
+      </c>
+      <c r="U2" s="15" t="str">
+        <f>"
+## Lektüre
+## Diskussion
+## Vorschau
+"&amp;G3</f>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Was ist die Religionswissenschaft?</v>
+      </c>
+      <c r="V2" s="15" t="str">
+        <f>_xlfn.CONCAT(S2:U2)</f>
+        <v>---
+layout: reveal
+title: 'Was machen wir hier?'
+author: 'Nathan Gibson'
+session: 1
+tags: [1,slides]
+category: slides
+image: candle.jpg
+parallaxBackgroundImage: 'assets/img/candle.jpg'
+---
+# Einführung in die Religionswissenschaft
+{: .r-fit-text}
+### Was machen wir hier?
+Wintersemester 2025/2026
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+objective
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Sich gegenseitig kennenlernen und unsere gegenseitige Ziele für den Kurs berücksichtigen.
+## Lektüre
+## Diskussion
+## Vorschau
+Was ist die Religionswissenschaft?</v>
+      </c>
     </row>
-    <row r="3" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="3">
         <v>2</v>
       </c>
@@ -902,38 +1040,46 @@
         <v>16</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="I3" t="str">
         <f t="shared" ref="I3:I16" si="4">B3 &amp; ". " &amp; E3 &amp; ": " &amp; G3</f>
-        <v>2. Religion als Gegenstand: Was ist Religion?</v>
+        <v>2. Religion als Gegenstand: Was ist die Religionswissenschaft?</v>
       </c>
       <c r="J3" s="3">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L16" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
-        <v>2-Definitionen</v>
+        <v>2-Religionswissenschaft</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s">
-        <v>73</v>
+        <v>96</v>
+      </c>
+      <c r="O3" t="s">
+        <v>97</v>
       </c>
       <c r="P3" t="str">
         <f t="shared" si="2"/>
         <v>[2]</v>
       </c>
-      <c r="Q3" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q3" s="15" t="str">
+        <f t="shared" ref="Q3:Q16" si="6">"---
+layout: post
+" &amp; B$1 &amp; ": " &amp; B3 &amp; "
+" &amp; P$1 &amp; ": " &amp; P3 &amp; "
+level: overview
+---"</f>
         <v>---
 layout: post
 session: 2
@@ -941,8 +1087,103 @@
 level: overview
 ---</v>
       </c>
+      <c r="R3" s="15" t="str">
+        <f t="shared" ref="R3:R16" si="7">_xlfn.REGEXREPLACE(D3,"\.md","-slides.md")</f>
+        <v>2025-10-20-2-slides.md</v>
+      </c>
+      <c r="S3" s="15" t="str">
+        <f t="shared" ref="S3:S16" si="8">"---
+layout: reveal
+title: '"&amp;G3&amp;"'
+author: 'Nathan Gibson'
+session: "&amp;B3&amp;"
+tags: ["&amp;B3&amp;",slides]
+category: slides
+image: "&amp;K3&amp;"
+parallaxBackgroundImage: 'assets/img/"&amp;K3&amp;"'
+---
+"</f>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Was ist die Religionswissenschaft?'
+author: 'Nathan Gibson'
+session: 2
+tags: [2,slides]
+category: slides
+image: religionen-lupe.jpg
+parallaxBackgroundImage: 'assets/img/religionen-lupe.jpg'
+---
+</v>
+      </c>
+      <c r="T3" s="15" t="str">
+        <f t="shared" ref="T3:T16" si="9">"# Einführung ins Judentum
+{: .r-fit-text}
+### "&amp;G3&amp;"
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+"&amp;N2&amp;"
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+"&amp;N3</f>
+        <v># Einführung ins Judentum
+{: .r-fit-text}
+### Was ist die Religionswissenschaft?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Sich gegenseitig kennenlernen und unsere gegenseitige Ziele für den Kurs berücksichtigen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die Bestimmung des Fachs Religionswissenschaft in seiner Breite und mit seinen Unterschieden zur Theologie erfassen.</v>
+      </c>
+      <c r="U3" s="15" t="str">
+        <f t="shared" ref="U3:U16" si="10">"
+## Lektüre
+## Diskussion
+## Vorschau
+"&amp;G4</f>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Was ist Religion?</v>
+      </c>
+      <c r="V3" s="15" t="str">
+        <f t="shared" ref="V3:V16" si="11">_xlfn.CONCAT(S3:U3)</f>
+        <v>---
+layout: reveal
+title: 'Was ist die Religionswissenschaft?'
+author: 'Nathan Gibson'
+session: 2
+tags: [2,slides]
+category: slides
+image: religionen-lupe.jpg
+parallaxBackgroundImage: 'assets/img/religionen-lupe.jpg'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Was ist die Religionswissenschaft?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Sich gegenseitig kennenlernen und unsere gegenseitige Ziele für den Kurs berücksichtigen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die Bestimmung des Fachs Religionswissenschaft in seiner Breite und mit seinen Unterschieden zur Theologie erfassen.
+## Lektüre
+## Diskussion
+## Vorschau
+Was ist Religion?</v>
+      </c>
     </row>
-    <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3">
         <v>3</v>
       </c>
@@ -957,38 +1198,41 @@
         <v>16</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I4" t="str">
         <f t="shared" si="4"/>
-        <v>3. Religion als Gegenstand: Was gilt als religiöses Ritual?</v>
+        <v>3. Religion als Gegenstand: Was ist Religion?</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" si="5"/>
-        <v>3-Ritual</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>65</v>
+        <v>3-Definitionen</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>60</v>
       </c>
       <c r="N4" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="O4" t="s">
+        <v>98</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
         <v>[3]</v>
       </c>
-      <c r="Q4" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q4" s="15" t="str">
+        <f t="shared" si="6"/>
         <v>---
 layout: post
 session: 3
@@ -996,8 +1240,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R4" s="15" t="str">
+        <f t="shared" si="7"/>
+        <v>2025-10-27-3-slides.md</v>
+      </c>
+      <c r="S4" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Was ist Religion?'
+author: 'Nathan Gibson'
+session: 3
+tags: [3,slides]
+category: slides
+image: magnifying-glass.jpg
+parallaxBackgroundImage: 'assets/img/magnifying-glass.jpg'
+---
+</v>
+      </c>
+      <c r="T4" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v># Einführung ins Judentum
+{: .r-fit-text}
+### Was ist Religion?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Die Bestimmung des Fachs Religionswissenschaft in seiner Breite und mit seinen Unterschieden zur Theologie erfassen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Verschiedene Definitionen von Religion unterscheiden können, was sie umfassen und wofür sie nützlich sein können.</v>
+      </c>
+      <c r="U4" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Was gilt als religiöses Ritual?</v>
+      </c>
+      <c r="V4" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v>---
+layout: reveal
+title: 'Was ist Religion?'
+author: 'Nathan Gibson'
+session: 3
+tags: [3,slides]
+category: slides
+image: magnifying-glass.jpg
+parallaxBackgroundImage: 'assets/img/magnifying-glass.jpg'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Was ist Religion?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Die Bestimmung des Fachs Religionswissenschaft in seiner Breite und mit seinen Unterschieden zur Theologie erfassen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Verschiedene Definitionen von Religion unterscheiden können, was sie umfassen und wofür sie nützlich sein können.
+## Lektüre
+## Diskussion
+## Vorschau
+Was gilt als religiöses Ritual?</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
         <v>4</v>
       </c>
@@ -1009,41 +1323,44 @@
         <v>2025-11-03-4.md</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I5" t="str">
         <f t="shared" si="4"/>
-        <v>4. Gruppen und Autorität: Wie bilden sich religiöse Gruppen und Autoritäten?</v>
+        <v>4. Religion als Gegenstand: Was gilt als religiöses Ritual?</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
-        <v>4-Gruppen</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>66</v>
+        <v>4-Ritual</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="N5" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="O5" t="s">
+        <v>99</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
         <v>[4]</v>
       </c>
-      <c r="Q5" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q5" s="15" t="str">
+        <f t="shared" si="6"/>
         <v>---
 layout: post
 session: 4
@@ -1051,8 +1368,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R5" s="15" t="str">
+        <f t="shared" si="7"/>
+        <v>2025-11-03-4-slides.md</v>
+      </c>
+      <c r="S5" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Was gilt als religiöses Ritual?'
+author: 'Nathan Gibson'
+session: 4
+tags: [4,slides]
+category: slides
+image: 02_Fussball.jpg
+parallaxBackgroundImage: 'assets/img/02_Fussball.jpg'
+---
+</v>
+      </c>
+      <c r="T5" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v># Einführung ins Judentum
+{: .r-fit-text}
+### Was gilt als religiöses Ritual?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Verschiedene Definitionen von Religion unterscheiden können, was sie umfassen und wofür sie nützlich sein können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Rituale auf drei Ebenen (Formen, Funktionen, Bedeutungen) anhand von Beispielen schildern können.</v>
+      </c>
+      <c r="U5" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Wie bilden sich religiöse Gruppen und Autoritäten?</v>
+      </c>
+      <c r="V5" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v>---
+layout: reveal
+title: 'Was gilt als religiöses Ritual?'
+author: 'Nathan Gibson'
+session: 4
+tags: [4,slides]
+category: slides
+image: 02_Fussball.jpg
+parallaxBackgroundImage: 'assets/img/02_Fussball.jpg'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Was gilt als religiöses Ritual?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Verschiedene Definitionen von Religion unterscheiden können, was sie umfassen und wofür sie nützlich sein können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Rituale auf drei Ebenen (Formen, Funktionen, Bedeutungen) anhand von Beispielen schildern können.
+## Lektüre
+## Diskussion
+## Vorschau
+Wie bilden sich religiöse Gruppen und Autoritäten?</v>
+      </c>
     </row>
-    <row r="6" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
         <v>5</v>
       </c>
@@ -1067,38 +1454,38 @@
         <v>17</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I6" t="str">
         <f t="shared" si="4"/>
-        <v>5. Gruppen und Autorität: Welche Rolle spielt Gender in der Religion?</v>
+        <v>5. Gruppen und Autorität: Wie bilden sich religiöse Gruppen und Autoritäten?</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
-        <v>5-Gender</v>
+        <v>5-Gruppen</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
         <v>[5]</v>
       </c>
-      <c r="Q6" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q6" s="15" t="str">
+        <f t="shared" si="6"/>
         <v>---
 layout: post
 session: 5
@@ -1106,8 +1493,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R6" s="15" t="str">
+        <f t="shared" si="7"/>
+        <v>2025-11-10-5-slides.md</v>
+      </c>
+      <c r="S6" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie bilden sich religiöse Gruppen und Autoritäten?'
+author: 'Nathan Gibson'
+session: 5
+tags: [5,slides]
+category: slides
+image: kaaba.jpg
+parallaxBackgroundImage: 'assets/img/kaaba.jpg'
+---
+</v>
+      </c>
+      <c r="T6" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v># Einführung ins Judentum
+{: .r-fit-text}
+### Wie bilden sich religiöse Gruppen und Autoritäten?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Rituale auf drei Ebenen (Formen, Funktionen, Bedeutungen) anhand von Beispielen schildern können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Historische und gegenwärtige Beispiele der Gruppenbildung anhand eines differenzierten Konzepts von "Meister/Jüngerschaft" erläutern können.</v>
+      </c>
+      <c r="U6" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Welche Rolle spielt Gender in der Religion?</v>
+      </c>
+      <c r="V6" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v>---
+layout: reveal
+title: 'Wie bilden sich religiöse Gruppen und Autoritäten?'
+author: 'Nathan Gibson'
+session: 5
+tags: [5,slides]
+category: slides
+image: kaaba.jpg
+parallaxBackgroundImage: 'assets/img/kaaba.jpg'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Wie bilden sich religiöse Gruppen und Autoritäten?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Rituale auf drei Ebenen (Formen, Funktionen, Bedeutungen) anhand von Beispielen schildern können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Historische und gegenwärtige Beispiele der Gruppenbildung anhand eines differenzierten Konzepts von "Meister/Jüngerschaft" erläutern können.
+## Lektüre
+## Diskussion
+## Vorschau
+Welche Rolle spielt Gender in der Religion?</v>
+      </c>
     </row>
-    <row r="7" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3">
         <v>6</v>
       </c>
@@ -1122,38 +1579,38 @@
         <v>17</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="4"/>
-        <v>6. Gruppen und Autorität: Wer oder was bestimmt die Orthodoxie?</v>
+        <v>6. Gruppen und Autorität: Welche Rolle spielt Gender in der Religion?</v>
       </c>
       <c r="J7" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L7" t="str">
         <f t="shared" si="5"/>
-        <v>6-Orthodoxie</v>
-      </c>
-      <c r="M7" s="12" t="s">
-        <v>77</v>
+        <v>6-Gender</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="N7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P7" t="str">
         <f t="shared" si="2"/>
         <v>[6]</v>
       </c>
-      <c r="Q7" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q7" s="15" t="str">
+        <f t="shared" si="6"/>
         <v>---
 layout: post
 session: 6
@@ -1161,8 +1618,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R7" s="15" t="str">
+        <f t="shared" si="7"/>
+        <v>2025-11-17-6-slides.md</v>
+      </c>
+      <c r="S7" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Welche Rolle spielt Gender in der Religion?'
+author: 'Nathan Gibson'
+session: 6
+tags: [6,slides]
+category: slides
+image: 04.MarabouWomen.jpg
+parallaxBackgroundImage: 'assets/img/04.MarabouWomen.jpg'
+---
+</v>
+      </c>
+      <c r="T7" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v># Einführung ins Judentum
+{: .r-fit-text}
+### Welche Rolle spielt Gender in der Religion?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Historische und gegenwärtige Beispiele der Gruppenbildung anhand eines differenzierten Konzepts von "Meister/Jüngerschaft" erläutern können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Ebenen der Genderforschung erläutern können, auf die die Religionswissenschaft grundlegend eingehen kann.</v>
+      </c>
+      <c r="U7" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Wer oder was bestimmt die Orthodoxie?</v>
+      </c>
+      <c r="V7" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v>---
+layout: reveal
+title: 'Welche Rolle spielt Gender in der Religion?'
+author: 'Nathan Gibson'
+session: 6
+tags: [6,slides]
+category: slides
+image: 04.MarabouWomen.jpg
+parallaxBackgroundImage: 'assets/img/04.MarabouWomen.jpg'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Welche Rolle spielt Gender in der Religion?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Historische und gegenwärtige Beispiele der Gruppenbildung anhand eines differenzierten Konzepts von "Meister/Jüngerschaft" erläutern können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Ebenen der Genderforschung erläutern können, auf die die Religionswissenschaft grundlegend eingehen kann.
+## Lektüre
+## Diskussion
+## Vorschau
+Wer oder was bestimmt die Orthodoxie?</v>
+      </c>
     </row>
-    <row r="8" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3">
         <v>7</v>
       </c>
@@ -1174,41 +1701,41 @@
         <v>2025-11-24-7.md</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" si="4"/>
-        <v>7. Materialität und Körper: Wie werden heilige Schriften überliefert?</v>
+        <v>7. Gruppen und Autorität: Wer oder was bestimmt die Orthodoxie?</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="K8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L8" t="str">
         <f t="shared" si="5"/>
-        <v>7-Schriften</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>68</v>
+        <v>7-Orthodoxie</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>75</v>
       </c>
       <c r="N8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P8" t="str">
         <f t="shared" si="2"/>
         <v>[7]</v>
       </c>
-      <c r="Q8" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q8" s="15" t="str">
+        <f t="shared" si="6"/>
         <v>---
 layout: post
 session: 7
@@ -1216,8 +1743,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R8" s="15" t="str">
+        <f t="shared" si="7"/>
+        <v>2025-11-24-7-slides.md</v>
+      </c>
+      <c r="S8" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wer oder was bestimmt die Orthodoxie?'
+author: 'Nathan Gibson'
+session: 7
+tags: [7,slides]
+category: slides
+image: yezidi.jpg
+parallaxBackgroundImage: 'assets/img/yezidi.jpg'
+---
+</v>
+      </c>
+      <c r="T8" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v># Einführung ins Judentum
+{: .r-fit-text}
+### Wer oder was bestimmt die Orthodoxie?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Ebenen der Genderforschung erläutern können, auf die die Religionswissenschaft grundlegend eingehen kann.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erklären können, wie Normativitätsansprüche in der Religionswissenschaft untersucht werden können.</v>
+      </c>
+      <c r="U8" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Wie werden heilige Schriften überliefert?</v>
+      </c>
+      <c r="V8" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v>---
+layout: reveal
+title: 'Wer oder was bestimmt die Orthodoxie?'
+author: 'Nathan Gibson'
+session: 7
+tags: [7,slides]
+category: slides
+image: yezidi.jpg
+parallaxBackgroundImage: 'assets/img/yezidi.jpg'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Wer oder was bestimmt die Orthodoxie?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Ebenen der Genderforschung erläutern können, auf die die Religionswissenschaft grundlegend eingehen kann.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erklären können, wie Normativitätsansprüche in der Religionswissenschaft untersucht werden können.
+## Lektüre
+## Diskussion
+## Vorschau
+Wie werden heilige Schriften überliefert?</v>
+      </c>
     </row>
-    <row r="9" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="3">
         <v>8</v>
       </c>
@@ -1232,38 +1829,38 @@
         <v>18</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="4"/>
-        <v>8. Materialität und Körper: Welche Rolle spielen materielle Objekte in der Religion?</v>
+        <v>8. Materialität und Körper: Wie werden heilige Schriften überliefert?</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="K9" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
-        <v>8-Objekte</v>
+        <v>8-Schriften</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
         <v>[8]</v>
       </c>
-      <c r="Q9" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q9" s="15" t="str">
+        <f t="shared" si="6"/>
         <v>---
 layout: post
 session: 8
@@ -1271,8 +1868,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R9" s="15" t="str">
+        <f t="shared" si="7"/>
+        <v>2025-12-01-8-slides.md</v>
+      </c>
+      <c r="S9" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie werden heilige Schriften überliefert?'
+author: 'Nathan Gibson'
+session: 8
+tags: [8,slides]
+category: slides
+image: synagogue-scroll.jpg
+parallaxBackgroundImage: 'assets/img/synagogue-scroll.jpg'
+---
+</v>
+      </c>
+      <c r="T9" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v># Einführung ins Judentum
+{: .r-fit-text}
+### Wie werden heilige Schriften überliefert?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Erklären können, wie Normativitätsansprüche in der Religionswissenschaft untersucht werden können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die mündliche und schriftliche Dynamik der abrahamitischen Religionen im Verhältnis zueinander zu beschreiben.</v>
+      </c>
+      <c r="U9" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Welche Rolle spielen materielle Objekte in der Religion?</v>
+      </c>
+      <c r="V9" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v>---
+layout: reveal
+title: 'Wie werden heilige Schriften überliefert?'
+author: 'Nathan Gibson'
+session: 8
+tags: [8,slides]
+category: slides
+image: synagogue-scroll.jpg
+parallaxBackgroundImage: 'assets/img/synagogue-scroll.jpg'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Wie werden heilige Schriften überliefert?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Erklären können, wie Normativitätsansprüche in der Religionswissenschaft untersucht werden können.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die mündliche und schriftliche Dynamik der abrahamitischen Religionen im Verhältnis zueinander zu beschreiben.
+## Lektüre
+## Diskussion
+## Vorschau
+Welche Rolle spielen materielle Objekte in der Religion?</v>
+      </c>
     </row>
-    <row r="10" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3">
         <v>9</v>
       </c>
@@ -1287,41 +1954,38 @@
         <v>18</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="4"/>
-        <v>9. Materialität und Körper: Welche Rolle spielen heilige Orte in der Religion?</v>
+        <v>9. Materialität und Körper: Welche Rolle spielen materielle Objekte in der Religion?</v>
       </c>
       <c r="J10" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="K10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L10" t="str">
         <f t="shared" si="5"/>
-        <v>9-Orte</v>
+        <v>9-Objekte</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N10" t="s">
-        <v>82</v>
-      </c>
-      <c r="O10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
         <v>[9]</v>
       </c>
-      <c r="Q10" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q10" s="15" t="str">
+        <f t="shared" si="6"/>
         <v>---
 layout: post
 session: 9
@@ -1329,8 +1993,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R10" s="15" t="str">
+        <f t="shared" si="7"/>
+        <v>2025-12-08-9-slides.md</v>
+      </c>
+      <c r="S10" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Welche Rolle spielen materielle Objekte in der Religion?'
+author: 'Nathan Gibson'
+session: 9
+tags: [9,slides]
+category: slides
+image: mosque.jpg
+parallaxBackgroundImage: 'assets/img/mosque.jpg'
+---
+</v>
+      </c>
+      <c r="T10" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v># Einführung ins Judentum
+{: .r-fit-text}
+### Welche Rolle spielen materielle Objekte in der Religion?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Die mündliche und schriftliche Dynamik der abrahamitischen Religionen im Verhältnis zueinander zu beschreiben.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erklären können, wie die Forschung an materiellen Objekten den Glauben an das Transzendente greifbar macht.</v>
+      </c>
+      <c r="U10" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Welche Rolle spielen heilige Orte in der Religion?</v>
+      </c>
+      <c r="V10" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v>---
+layout: reveal
+title: 'Welche Rolle spielen materielle Objekte in der Religion?'
+author: 'Nathan Gibson'
+session: 9
+tags: [9,slides]
+category: slides
+image: mosque.jpg
+parallaxBackgroundImage: 'assets/img/mosque.jpg'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Welche Rolle spielen materielle Objekte in der Religion?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Die mündliche und schriftliche Dynamik der abrahamitischen Religionen im Verhältnis zueinander zu beschreiben.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erklären können, wie die Forschung an materiellen Objekten den Glauben an das Transzendente greifbar macht.
+## Lektüre
+## Diskussion
+## Vorschau
+Welche Rolle spielen heilige Orte in der Religion?</v>
+      </c>
     </row>
-    <row r="11" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3">
         <v>10</v>
       </c>
@@ -1344,37 +2078,42 @@
       <c r="E11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>90</v>
+      <c r="F11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" t="s">
+        <v>42</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
-        <v>10. Materialität und Körper: Kursbesuch: Kunst (Shahid Alam)</v>
+        <v>10. Materialität und Körper: Welche Rolle spielen heilige Orte in der Religion?</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" t="s">
         <v>55</v>
       </c>
       <c r="L11" t="str">
         <f t="shared" si="5"/>
-        <v>10-Kunst</v>
-      </c>
-      <c r="M11" s="9"/>
+        <v>10-Orte</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="N11" t="s">
-        <v>84</v>
+        <v>80</v>
+      </c>
+      <c r="O11" t="s">
+        <v>81</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
         <v>[10]</v>
       </c>
-      <c r="Q11" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q11" s="15" t="str">
+        <f t="shared" si="6"/>
         <v>---
 layout: post
 session: 10
@@ -1382,8 +2121,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R11" s="15" t="str">
+        <f t="shared" si="7"/>
+        <v>2025-12-15-10-slides.md</v>
+      </c>
+      <c r="S11" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Welche Rolle spielen heilige Orte in der Religion?'
+author: 'Nathan Gibson'
+session: 10
+tags: [10,slides]
+category: slides
+image: madaba-map.jpg
+parallaxBackgroundImage: 'assets/img/madaba-map.jpg'
+---
+</v>
+      </c>
+      <c r="T11" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v># Einführung ins Judentum
+{: .r-fit-text}
+### Welche Rolle spielen heilige Orte in der Religion?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Erklären können, wie die Forschung an materiellen Objekten den Glauben an das Transzendente greifbar macht.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erklären können, auf welche Weise Orte sakrale Bedeutung erlangen, und diese Bedeutung anhand jüdischer, christlicher und islamischer Beispiele erläutern.</v>
+      </c>
+      <c r="U11" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Welche Wirkung hat die religiöse Praxis auf den Körper?</v>
+      </c>
+      <c r="V11" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v>---
+layout: reveal
+title: 'Welche Rolle spielen heilige Orte in der Religion?'
+author: 'Nathan Gibson'
+session: 10
+tags: [10,slides]
+category: slides
+image: madaba-map.jpg
+parallaxBackgroundImage: 'assets/img/madaba-map.jpg'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Welche Rolle spielen heilige Orte in der Religion?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Erklären können, wie die Forschung an materiellen Objekten den Glauben an das Transzendente greifbar macht.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erklären können, auf welche Weise Orte sakrale Bedeutung erlangen, und diese Bedeutung anhand jüdischer, christlicher und islamischer Beispiele erläutern.
+## Lektüre
+## Diskussion
+## Vorschau
+Welche Wirkung hat die religiöse Praxis auf den Körper?</v>
+      </c>
     </row>
-    <row r="12" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3">
         <v>11</v>
       </c>
@@ -1398,10 +2207,10 @@
         <v>18</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="4"/>
@@ -1412,27 +2221,27 @@
         <v>11</v>
       </c>
       <c r="K12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L12" t="str">
         <f t="shared" si="5"/>
         <v>11-Körper</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="O12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
         <v>[11]</v>
       </c>
-      <c r="Q12" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q12" s="15" t="str">
+        <f t="shared" si="6"/>
         <v>---
 layout: post
 session: 11
@@ -1440,8 +2249,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R12" s="15" t="str">
+        <f t="shared" si="7"/>
+        <v>2026-01-12-11-slides.md</v>
+      </c>
+      <c r="S12" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Welche Wirkung hat die religiöse Praxis auf den Körper?'
+author: 'Nathan Gibson'
+session: 11
+tags: [11,slides]
+category: slides
+image: dhanvantari.jpg
+parallaxBackgroundImage: 'assets/img/dhanvantari.jpg'
+---
+</v>
+      </c>
+      <c r="T12" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v># Einführung ins Judentum
+{: .r-fit-text}
+### Welche Wirkung hat die religiöse Praxis auf den Körper?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Erklären können, auf welche Weise Orte sakrale Bedeutung erlangen, und diese Bedeutung anhand jüdischer, christlicher und islamischer Beispiele erläutern.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Religionspsychologische Ansätze zur Krankheit und Heilung schildern.</v>
+      </c>
+      <c r="U12" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Wie wird Religion digital untersucht?</v>
+      </c>
+      <c r="V12" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v>---
+layout: reveal
+title: 'Welche Wirkung hat die religiöse Praxis auf den Körper?'
+author: 'Nathan Gibson'
+session: 11
+tags: [11,slides]
+category: slides
+image: dhanvantari.jpg
+parallaxBackgroundImage: 'assets/img/dhanvantari.jpg'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Welche Wirkung hat die religiöse Praxis auf den Körper?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Erklären können, auf welche Weise Orte sakrale Bedeutung erlangen, und diese Bedeutung anhand jüdischer, christlicher und islamischer Beispiele erläutern.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Religionspsychologische Ansätze zur Krankheit und Heilung schildern.
+## Lektüre
+## Diskussion
+## Vorschau
+Wie wird Religion digital untersucht?</v>
+      </c>
     </row>
-    <row r="13" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3">
         <v>12</v>
       </c>
@@ -1456,10 +2335,10 @@
         <v>19</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="4"/>
@@ -1470,27 +2349,27 @@
         <v>12</v>
       </c>
       <c r="K13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
         <v>12-Digitalisierung</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
         <v>[12]</v>
       </c>
-      <c r="Q13" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q13" s="15" t="str">
+        <f t="shared" si="6"/>
         <v>---
 layout: post
 session: 12
@@ -1498,8 +2377,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R13" s="15" t="str">
+        <f t="shared" si="7"/>
+        <v>2026-01-19-12-slides.md</v>
+      </c>
+      <c r="S13" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie wird Religion digital untersucht?'
+author: 'Nathan Gibson'
+session: 12
+tags: [12,slides]
+category: slides
+image: digital.jpg
+parallaxBackgroundImage: 'assets/img/digital.jpg'
+---
+</v>
+      </c>
+      <c r="T13" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v># Einführung ins Judentum
+{: .r-fit-text}
+### Wie wird Religion digital untersucht?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Religionspsychologische Ansätze zur Krankheit und Heilung schildern.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Verständnis dafür zeigen, wie religiöse Identität, Gemeinschaft und Autorität in Online- und Offline-Umgebungen miteinander verwoben sind.</v>
+      </c>
+      <c r="U13" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Wie sollte religiöser Extremismus verstanden werden?</v>
+      </c>
+      <c r="V13" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v>---
+layout: reveal
+title: 'Wie wird Religion digital untersucht?'
+author: 'Nathan Gibson'
+session: 12
+tags: [12,slides]
+category: slides
+image: digital.jpg
+parallaxBackgroundImage: 'assets/img/digital.jpg'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Wie wird Religion digital untersucht?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Religionspsychologische Ansätze zur Krankheit und Heilung schildern.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Verständnis dafür zeigen, wie religiöse Identität, Gemeinschaft und Autorität in Online- und Offline-Umgebungen miteinander verwoben sind.
+## Lektüre
+## Diskussion
+## Vorschau
+Wie sollte religiöser Extremismus verstanden werden?</v>
+      </c>
     </row>
-    <row r="14" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="5">
         <v>13</v>
       </c>
@@ -1514,10 +2463,10 @@
         <v>19</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="4"/>
@@ -1528,27 +2477,27 @@
         <v>13</v>
       </c>
       <c r="K14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L14" t="str">
         <f t="shared" si="5"/>
         <v>13-Extremismus</v>
       </c>
-      <c r="M14" s="15" t="s">
-        <v>93</v>
+      <c r="M14" s="13" t="s">
+        <v>89</v>
       </c>
       <c r="N14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
         <v>[13]</v>
       </c>
-      <c r="Q14" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q14" s="15" t="str">
+        <f t="shared" si="6"/>
         <v>---
 layout: post
 session: 13
@@ -1556,8 +2505,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R14" s="15" t="str">
+        <f t="shared" si="7"/>
+        <v>2026-01-26-13-slides.md</v>
+      </c>
+      <c r="S14" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie sollte religiöser Extremismus verstanden werden?'
+author: 'Nathan Gibson'
+session: 13
+tags: [13,slides]
+category: slides
+image: 12_iranischeSchiiten.jpeg
+parallaxBackgroundImage: 'assets/img/12_iranischeSchiiten.jpeg'
+---
+</v>
+      </c>
+      <c r="T14" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v># Einführung ins Judentum
+{: .r-fit-text}
+### Wie sollte religiöser Extremismus verstanden werden?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Verständnis dafür zeigen, wie religiöse Identität, Gemeinschaft und Autorität in Online- und Offline-Umgebungen miteinander verwoben sind.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Fundamentalismus, Radikalisierung und Extremismus definieren und Beispiele für jeden Begriff geben.</v>
+      </c>
+      <c r="U14" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?</v>
+      </c>
+      <c r="V14" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v>---
+layout: reveal
+title: 'Wie sollte religiöser Extremismus verstanden werden?'
+author: 'Nathan Gibson'
+session: 13
+tags: [13,slides]
+category: slides
+image: 12_iranischeSchiiten.jpeg
+parallaxBackgroundImage: 'assets/img/12_iranischeSchiiten.jpeg'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Wie sollte religiöser Extremismus verstanden werden?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Verständnis dafür zeigen, wie religiöse Identität, Gemeinschaft und Autorität in Online- und Offline-Umgebungen miteinander verwoben sind.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Fundamentalismus, Radikalisierung und Extremismus definieren und Beispiele für jeden Begriff geben.
+## Lektüre
+## Diskussion
+## Vorschau
+Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?</v>
+      </c>
     </row>
-    <row r="15" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="5">
         <v>14</v>
       </c>
@@ -1572,10 +2591,10 @@
         <v>19</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" si="4"/>
@@ -1586,24 +2605,24 @@
         <v>14</v>
       </c>
       <c r="K15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L15" t="str">
         <f t="shared" si="5"/>
         <v>14-Interreligiös</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N15" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>
         <v>[14]</v>
       </c>
-      <c r="Q15" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q15" s="15" t="str">
+        <f t="shared" si="6"/>
         <v>---
 layout: post
 session: 14
@@ -1611,8 +2630,78 @@
 level: overview
 ---</v>
       </c>
+      <c r="R15" s="15" t="str">
+        <f t="shared" si="7"/>
+        <v>2026-02-02-14-slides.md</v>
+      </c>
+      <c r="S15" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?'
+author: 'Nathan Gibson'
+session: 14
+tags: [14,slides]
+category: slides
+image: interreligious-conversation.png
+parallaxBackgroundImage: 'assets/img/interreligious-conversation.png'
+---
+</v>
+      </c>
+      <c r="T15" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v># Einführung ins Judentum
+{: .r-fit-text}
+### Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Fundamentalismus, Radikalisierung und Extremismus definieren und Beispiele für jeden Begriff geben.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Überlegen und erklären können, inwieweit religionswissenschaftliche Ansätze zum interreligiösen Dialog beitragen können, sollen und dürfen.</v>
+      </c>
+      <c r="U15" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+Wie gehe ich mit dem erworbenen Wissen um?</v>
+      </c>
+      <c r="V15" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v>---
+layout: reveal
+title: 'Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?'
+author: 'Nathan Gibson'
+session: 14
+tags: [14,slides]
+category: slides
+image: interreligious-conversation.png
+parallaxBackgroundImage: 'assets/img/interreligious-conversation.png'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Fundamentalismus, Radikalisierung und Extremismus definieren und Beispiele für jeden Begriff geben.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Überlegen und erklären können, inwieweit religionswissenschaftliche Ansätze zum interreligiösen Dialog beitragen können, sollen und dürfen.
+## Lektüre
+## Diskussion
+## Vorschau
+Wie gehe ich mit dem erworbenen Wissen um?</v>
+      </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="5">
         <v>15</v>
       </c>
@@ -1627,10 +2716,10 @@
         <v>19</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I16" t="str">
         <f t="shared" si="4"/>
@@ -1641,24 +2730,93 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L16" t="str">
         <f t="shared" si="5"/>
         <v>15-Abschluss</v>
       </c>
       <c r="P16" t="str">
-        <f t="shared" ref="P16" si="6">"["&amp;B16&amp;"]"</f>
+        <f t="shared" ref="P16" si="12">"["&amp;B16&amp;"]"</f>
         <v>[15]</v>
       </c>
-      <c r="Q16" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q16" s="15" t="str">
+        <f t="shared" si="6"/>
         <v>---
 layout: post
 session: 15
 tags: [15]
 level: overview
 ---</v>
+      </c>
+      <c r="R16" s="15" t="str">
+        <f t="shared" si="7"/>
+        <v>2026-02-09-15-slides.md</v>
+      </c>
+      <c r="S16" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie gehe ich mit dem erworbenen Wissen um?'
+author: 'Nathan Gibson'
+session: 15
+tags: [15,slides]
+category: slides
+image: girl-bridge.jpg
+parallaxBackgroundImage: 'assets/img/girl-bridge.jpg'
+---
+</v>
+      </c>
+      <c r="T16" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"># Einführung ins Judentum
+{: .r-fit-text}
+### Wie gehe ich mit dem erworbenen Wissen um?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Überlegen und erklären können, inwieweit religionswissenschaftliche Ansätze zum interreligiösen Dialog beitragen können, sollen und dürfen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+</v>
+      </c>
+      <c r="U16" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">
+## Lektüre
+## Diskussion
+## Vorschau
+</v>
+      </c>
+      <c r="V16" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">---
+layout: reveal
+title: 'Wie gehe ich mit dem erworbenen Wissen um?'
+author: 'Nathan Gibson'
+session: 15
+tags: [15,slides]
+category: slides
+image: girl-bridge.jpg
+parallaxBackgroundImage: 'assets/img/girl-bridge.jpg'
+---
+# Einführung ins Judentum
+{: .r-fit-text}
+### Wie gehe ich mit dem erworbenen Wissen um?
+Sommersemester 2025
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Überlegen und erklären können, inwieweit religionswissenschaftliche Ansätze zum interreligiösen Dialog beitragen können, sollen und dürfen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+## Lektüre
+## Diskussion
+## Vorschau
+</v>
       </c>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.2">

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0BEE00-AAB3-2241-97AC-C7ECDA762E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995AF400-B8BE-2A4E-A11C-999D816B2525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -872,7 +872,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -958,7 +958,8 @@
 </v>
       </c>
       <c r="T2" s="15" t="str">
-        <f>"# Einführung in die Religionswissenschaft
+        <f>"# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### "&amp;G2&amp;"
 Wintersemester 2025/2026
@@ -970,7 +971,8 @@
 ## Einleitung
 ## Heutiges Lernziel
 "&amp;N2</f>
-        <v># Einführung in die Religionswissenschaft
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Was machen wir hier?
 Wintersemester 2025/2026
@@ -1007,7 +1009,8 @@
 image: candle.jpg
 parallaxBackgroundImage: 'assets/img/candle.jpg'
 ---
-# Einführung in die Religionswissenschaft
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Was machen wir hier?
 Wintersemester 2025/2026
@@ -1025,7 +1028,7 @@
 Was ist die Religionswissenschaft?</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="3">
         <v>2</v>
       </c>
@@ -1116,10 +1119,11 @@
 </v>
       </c>
       <c r="T3" s="15" t="str">
-        <f t="shared" ref="T3:T16" si="9">"# Einführung ins Judentum
+        <f t="shared" ref="T3:T16" si="9">"# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### "&amp;G3&amp;"
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 "&amp;N2&amp;"
@@ -1128,10 +1132,11 @@
 ## Einleitung
 ## Heutiges Lernziel
 "&amp;N3</f>
-        <v># Einführung ins Judentum
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Was ist die Religionswissenschaft?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Sich gegenseitig kennenlernen und unsere gegenseitige Ziele für den Kurs berücksichtigen.
@@ -1165,10 +1170,11 @@
 image: religionen-lupe.jpg
 parallaxBackgroundImage: 'assets/img/religionen-lupe.jpg'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Was ist die Religionswissenschaft?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Sich gegenseitig kennenlernen und unsere gegenseitige Ziele für den Kurs berücksichtigen.
@@ -1183,7 +1189,7 @@
 Was ist Religion?</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3">
         <v>3</v>
       </c>
@@ -1260,10 +1266,11 @@
       </c>
       <c r="T4" s="15" t="str">
         <f t="shared" si="9"/>
-        <v># Einführung ins Judentum
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Was ist Religion?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Die Bestimmung des Fachs Religionswissenschaft in seiner Breite und mit seinen Unterschieden zur Theologie erfassen.
@@ -1293,10 +1300,11 @@
 image: magnifying-glass.jpg
 parallaxBackgroundImage: 'assets/img/magnifying-glass.jpg'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Was ist Religion?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Die Bestimmung des Fachs Religionswissenschaft in seiner Breite und mit seinen Unterschieden zur Theologie erfassen.
@@ -1311,7 +1319,7 @@
 Was gilt als religiöses Ritual?</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
         <v>4</v>
       </c>
@@ -1388,10 +1396,11 @@
       </c>
       <c r="T5" s="15" t="str">
         <f t="shared" si="9"/>
-        <v># Einführung ins Judentum
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Was gilt als religiöses Ritual?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Verschiedene Definitionen von Religion unterscheiden können, was sie umfassen und wofür sie nützlich sein können.
@@ -1421,10 +1430,11 @@
 image: 02_Fussball.jpg
 parallaxBackgroundImage: 'assets/img/02_Fussball.jpg'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Was gilt als religiöses Ritual?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Verschiedene Definitionen von Religion unterscheiden können, was sie umfassen und wofür sie nützlich sein können.
@@ -1439,7 +1449,7 @@
 Wie bilden sich religiöse Gruppen und Autoritäten?</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
         <v>5</v>
       </c>
@@ -1513,10 +1523,11 @@
       </c>
       <c r="T6" s="15" t="str">
         <f t="shared" si="9"/>
-        <v># Einführung ins Judentum
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Wie bilden sich religiöse Gruppen und Autoritäten?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Rituale auf drei Ebenen (Formen, Funktionen, Bedeutungen) anhand von Beispielen schildern können.
@@ -1546,10 +1557,11 @@
 image: kaaba.jpg
 parallaxBackgroundImage: 'assets/img/kaaba.jpg'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Wie bilden sich religiöse Gruppen und Autoritäten?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Rituale auf drei Ebenen (Formen, Funktionen, Bedeutungen) anhand von Beispielen schildern können.
@@ -1564,7 +1576,7 @@
 Welche Rolle spielt Gender in der Religion?</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3">
         <v>6</v>
       </c>
@@ -1638,10 +1650,11 @@
       </c>
       <c r="T7" s="15" t="str">
         <f t="shared" si="9"/>
-        <v># Einführung ins Judentum
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Welche Rolle spielt Gender in der Religion?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Historische und gegenwärtige Beispiele der Gruppenbildung anhand eines differenzierten Konzepts von "Meister/Jüngerschaft" erläutern können.
@@ -1671,10 +1684,11 @@
 image: 04.MarabouWomen.jpg
 parallaxBackgroundImage: 'assets/img/04.MarabouWomen.jpg'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Welche Rolle spielt Gender in der Religion?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Historische und gegenwärtige Beispiele der Gruppenbildung anhand eines differenzierten Konzepts von "Meister/Jüngerschaft" erläutern können.
@@ -1689,7 +1703,7 @@
 Wer oder was bestimmt die Orthodoxie?</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3">
         <v>7</v>
       </c>
@@ -1763,10 +1777,11 @@
       </c>
       <c r="T8" s="15" t="str">
         <f t="shared" si="9"/>
-        <v># Einführung ins Judentum
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Wer oder was bestimmt die Orthodoxie?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Ebenen der Genderforschung erläutern können, auf die die Religionswissenschaft grundlegend eingehen kann.
@@ -1796,10 +1811,11 @@
 image: yezidi.jpg
 parallaxBackgroundImage: 'assets/img/yezidi.jpg'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Wer oder was bestimmt die Orthodoxie?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Ebenen der Genderforschung erläutern können, auf die die Religionswissenschaft grundlegend eingehen kann.
@@ -1814,7 +1830,7 @@
 Wie werden heilige Schriften überliefert?</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="3">
         <v>8</v>
       </c>
@@ -1888,10 +1904,11 @@
       </c>
       <c r="T9" s="15" t="str">
         <f t="shared" si="9"/>
-        <v># Einführung ins Judentum
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Wie werden heilige Schriften überliefert?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Erklären können, wie Normativitätsansprüche in der Religionswissenschaft untersucht werden können.
@@ -1921,10 +1938,11 @@
 image: synagogue-scroll.jpg
 parallaxBackgroundImage: 'assets/img/synagogue-scroll.jpg'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Wie werden heilige Schriften überliefert?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Erklären können, wie Normativitätsansprüche in der Religionswissenschaft untersucht werden können.
@@ -1939,7 +1957,7 @@
 Welche Rolle spielen materielle Objekte in der Religion?</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3">
         <v>9</v>
       </c>
@@ -2013,10 +2031,11 @@
       </c>
       <c r="T10" s="15" t="str">
         <f t="shared" si="9"/>
-        <v># Einführung ins Judentum
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Welche Rolle spielen materielle Objekte in der Religion?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Die mündliche und schriftliche Dynamik der abrahamitischen Religionen im Verhältnis zueinander zu beschreiben.
@@ -2046,10 +2065,11 @@
 image: mosque.jpg
 parallaxBackgroundImage: 'assets/img/mosque.jpg'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Welche Rolle spielen materielle Objekte in der Religion?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Die mündliche und schriftliche Dynamik der abrahamitischen Religionen im Verhältnis zueinander zu beschreiben.
@@ -2064,7 +2084,7 @@
 Welche Rolle spielen heilige Orte in der Religion?</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3">
         <v>10</v>
       </c>
@@ -2141,10 +2161,11 @@
       </c>
       <c r="T11" s="15" t="str">
         <f t="shared" si="9"/>
-        <v># Einführung ins Judentum
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Welche Rolle spielen heilige Orte in der Religion?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Erklären können, wie die Forschung an materiellen Objekten den Glauben an das Transzendente greifbar macht.
@@ -2174,10 +2195,11 @@
 image: madaba-map.jpg
 parallaxBackgroundImage: 'assets/img/madaba-map.jpg'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Welche Rolle spielen heilige Orte in der Religion?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Erklären können, wie die Forschung an materiellen Objekten den Glauben an das Transzendente greifbar macht.
@@ -2192,7 +2214,7 @@
 Welche Wirkung hat die religiöse Praxis auf den Körper?</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3">
         <v>11</v>
       </c>
@@ -2269,10 +2291,11 @@
       </c>
       <c r="T12" s="15" t="str">
         <f t="shared" si="9"/>
-        <v># Einführung ins Judentum
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Welche Wirkung hat die religiöse Praxis auf den Körper?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Erklären können, auf welche Weise Orte sakrale Bedeutung erlangen, und diese Bedeutung anhand jüdischer, christlicher und islamischer Beispiele erläutern.
@@ -2302,10 +2325,11 @@
 image: dhanvantari.jpg
 parallaxBackgroundImage: 'assets/img/dhanvantari.jpg'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Welche Wirkung hat die religiöse Praxis auf den Körper?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Erklären können, auf welche Weise Orte sakrale Bedeutung erlangen, und diese Bedeutung anhand jüdischer, christlicher und islamischer Beispiele erläutern.
@@ -2320,7 +2344,7 @@
 Wie wird Religion digital untersucht?</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3">
         <v>12</v>
       </c>
@@ -2397,10 +2421,11 @@
       </c>
       <c r="T13" s="15" t="str">
         <f t="shared" si="9"/>
-        <v># Einführung ins Judentum
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Wie wird Religion digital untersucht?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Religionspsychologische Ansätze zur Krankheit und Heilung schildern.
@@ -2430,10 +2455,11 @@
 image: digital.jpg
 parallaxBackgroundImage: 'assets/img/digital.jpg'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Wie wird Religion digital untersucht?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Religionspsychologische Ansätze zur Krankheit und Heilung schildern.
@@ -2448,7 +2474,7 @@
 Wie sollte religiöser Extremismus verstanden werden?</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="5">
         <v>13</v>
       </c>
@@ -2525,10 +2551,11 @@
       </c>
       <c r="T14" s="15" t="str">
         <f t="shared" si="9"/>
-        <v># Einführung ins Judentum
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Wie sollte religiöser Extremismus verstanden werden?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Verständnis dafür zeigen, wie religiöse Identität, Gemeinschaft und Autorität in Online- und Offline-Umgebungen miteinander verwoben sind.
@@ -2558,10 +2585,11 @@
 image: 12_iranischeSchiiten.jpeg
 parallaxBackgroundImage: 'assets/img/12_iranischeSchiiten.jpeg'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Wie sollte religiöser Extremismus verstanden werden?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Verständnis dafür zeigen, wie religiöse Identität, Gemeinschaft und Autorität in Online- und Offline-Umgebungen miteinander verwoben sind.
@@ -2576,7 +2604,7 @@
 Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="5">
         <v>14</v>
       </c>
@@ -2650,10 +2678,11 @@
       </c>
       <c r="T15" s="15" t="str">
         <f t="shared" si="9"/>
-        <v># Einführung ins Judentum
+        <v># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Fundamentalismus, Radikalisierung und Extremismus definieren und Beispiele für jeden Begriff geben.
@@ -2683,10 +2712,11 @@
 image: interreligious-conversation.png
 parallaxBackgroundImage: 'assets/img/interreligious-conversation.png'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Fundamentalismus, Radikalisierung und Extremismus definieren und Beispiele für jeden Begriff geben.
@@ -2701,7 +2731,7 @@
 Wie gehe ich mit dem erworbenen Wissen um?</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="5">
         <v>15</v>
       </c>
@@ -2769,10 +2799,11 @@
       </c>
       <c r="T16" s="15" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"># Einführung ins Judentum
+        <v xml:space="preserve"># Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Wie gehe ich mit dem erworbenen Wissen um?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Überlegen und erklären können, inwieweit religionswissenschaftliche Ansätze zum interreligiösen Dialog beitragen können, sollen und dürfen.
@@ -2802,10 +2833,11 @@
 image: girl-bridge.jpg
 parallaxBackgroundImage: 'assets/img/girl-bridge.jpg'
 ---
-# Einführung ins Judentum
+# Einführung in die 
+### Religionswissenschaft
 {: .r-fit-text}
 ### Wie gehe ich mit dem erworbenen Wissen um?
-Sommersemester 2025
+Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
 Überlegen und erklären können, inwieweit religionswissenschaftliche Ansätze zum interreligiösen Dialog beitragen können, sollen und dürfen.

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995AF400-B8BE-2A4E-A11C-999D816B2525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE2905A-1A08-5D46-AD7A-F609D1AE91CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -227,9 +227,6 @@
     <t>brombergerFussballAlsWeltsicht2003</t>
   </si>
   <si>
-    <t>rengerIII7MeisterJuengerUnd2012</t>
-  </si>
-  <si>
     <t>gemmekeMaraboutWomenDakar2009</t>
   </si>
   <si>
@@ -348,6 +345,9 @@
   </si>
   <si>
     <t>slide-content</t>
+  </si>
+  <si>
+    <t>freudenbergII1CharismaGenese2025</t>
   </si>
 </sst>
 </file>
@@ -359,9 +359,16 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -443,18 +450,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -464,20 +471,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -848,7 +856,7 @@
         <v>11</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>12</v>
@@ -857,19 +865,19 @@
         <v>13</v>
       </c>
       <c r="R1" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="S1" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="T1" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="U1" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="V1" s="14" t="s">
         <v>103</v>
-      </c>
-      <c r="V1" s="14" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -909,7 +917,7 @@
         <v>1-Vorstellung</v>
       </c>
       <c r="N2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P15" si="2">"["&amp;B2&amp;"]"</f>
@@ -1043,10 +1051,10 @@
         <v>16</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" t="s">
         <v>91</v>
-      </c>
-      <c r="G3" t="s">
-        <v>92</v>
       </c>
       <c r="I3" t="str">
         <f t="shared" ref="I3:I16" si="4">B3 &amp; ". " &amp; E3 &amp; ": " &amp; G3</f>
@@ -1057,20 +1065,20 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L16" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-Religionswissenschaft</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N3" t="s">
+        <v>95</v>
+      </c>
+      <c r="O3" t="s">
         <v>96</v>
-      </c>
-      <c r="O3" t="s">
-        <v>97</v>
       </c>
       <c r="P3" t="str">
         <f t="shared" si="2"/>
@@ -1228,10 +1236,10 @@
         <v>60</v>
       </c>
       <c r="N4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1358,10 +1366,10 @@
         <v>63</v>
       </c>
       <c r="N5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1484,11 +1492,11 @@
         <f t="shared" si="5"/>
         <v>5-Gruppen</v>
       </c>
-      <c r="M6" s="9" t="s">
-        <v>64</v>
+      <c r="M6" s="16" t="s">
+        <v>104</v>
       </c>
       <c r="N6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1612,10 +1620,10 @@
         <v>6-Gender</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P7" t="str">
         <f t="shared" si="2"/>
@@ -1739,10 +1747,10 @@
         <v>7-Orthodoxie</v>
       </c>
       <c r="M8" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="N8" t="s">
         <v>75</v>
-      </c>
-      <c r="N8" t="s">
-        <v>76</v>
       </c>
       <c r="P8" t="str">
         <f t="shared" si="2"/>
@@ -1866,10 +1874,10 @@
         <v>8-Schriften</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -1993,10 +2001,10 @@
         <v>9-Objekte</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
@@ -2120,13 +2128,13 @@
         <v>10-Orte</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N11" t="s">
+        <v>79</v>
+      </c>
+      <c r="O11" t="s">
         <v>80</v>
-      </c>
-      <c r="O11" t="s">
-        <v>81</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -2250,13 +2258,13 @@
         <v>11-Körper</v>
       </c>
       <c r="M12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="N12" t="s">
         <v>82</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>83</v>
-      </c>
-      <c r="O12" t="s">
-        <v>84</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
@@ -2380,13 +2388,13 @@
         <v>12-Digitalisierung</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -2510,13 +2518,13 @@
         <v>13-Extremismus</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N14" t="s">
+        <v>86</v>
+      </c>
+      <c r="O14" t="s">
         <v>87</v>
-      </c>
-      <c r="O14" t="s">
-        <v>88</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -2640,10 +2648,10 @@
         <v>14-Interreligiös</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE2905A-1A08-5D46-AD7A-F609D1AE91CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C56B14-8839-384D-B428-173CF64A7887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -251,9 +251,6 @@
     <t>Rituale auf drei Ebenen (Formen, Funktionen, Bedeutungen) anhand von Beispielen schildern können.</t>
   </si>
   <si>
-    <t>Historische und gegenwärtige Beispiele der Gruppenbildung anhand eines differenzierten Konzepts von "Meister/Jüngerschaft" erläutern können.</t>
-  </si>
-  <si>
     <t>Ebenen der Genderforschung erläutern können, auf die die Religionswissenschaft grundlegend eingehen kann.</t>
   </si>
   <si>
@@ -348,6 +345,9 @@
   </si>
   <si>
     <t>freudenbergII1CharismaGenese2025</t>
+  </si>
+  <si>
+    <t>Die Gruppenbildung durch die Genese, der Erhalt und die Veralltäglichung des Charismas mit historischen und gegenwärtigen Beispielen erläutern können.</t>
   </si>
 </sst>
 </file>
@@ -856,7 +856,7 @@
         <v>11</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>12</v>
@@ -865,19 +865,19 @@
         <v>13</v>
       </c>
       <c r="R1" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="S1" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="T1" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="U1" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="V1" s="14" t="s">
         <v>102</v>
-      </c>
-      <c r="V1" s="14" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -917,7 +917,7 @@
         <v>1-Vorstellung</v>
       </c>
       <c r="N2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P15" si="2">"["&amp;B2&amp;"]"</f>
@@ -1051,10 +1051,10 @@
         <v>16</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" t="s">
         <v>90</v>
-      </c>
-      <c r="G3" t="s">
-        <v>91</v>
       </c>
       <c r="I3" t="str">
         <f t="shared" ref="I3:I16" si="4">B3 &amp; ". " &amp; E3 &amp; ": " &amp; G3</f>
@@ -1065,20 +1065,20 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L16" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-Religionswissenschaft</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O3" t="s">
         <v>95</v>
-      </c>
-      <c r="O3" t="s">
-        <v>96</v>
       </c>
       <c r="P3" t="str">
         <f t="shared" si="2"/>
@@ -1239,7 +1239,7 @@
         <v>70</v>
       </c>
       <c r="O4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1369,7 +1369,7 @@
         <v>71</v>
       </c>
       <c r="O5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1493,10 +1493,10 @@
         <v>5-Gruppen</v>
       </c>
       <c r="M6" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="N6" t="s">
         <v>104</v>
-      </c>
-      <c r="N6" t="s">
-        <v>72</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1543,7 +1543,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Historische und gegenwärtige Beispiele der Gruppenbildung anhand eines differenzierten Konzepts von "Meister/Jüngerschaft" erläutern können.</v>
+Die Gruppenbildung durch die Genese, der Erhalt und die Veralltäglichung des Charismas mit historischen und gegenwärtigen Beispielen erläutern können.</v>
       </c>
       <c r="U6" s="15" t="str">
         <f t="shared" si="10"/>
@@ -1577,7 +1577,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Historische und gegenwärtige Beispiele der Gruppenbildung anhand eines differenzierten Konzepts von "Meister/Jüngerschaft" erläutern können.
+Die Gruppenbildung durch die Genese, der Erhalt und die Veralltäglichung des Charismas mit historischen und gegenwärtigen Beispielen erläutern können.
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -1623,7 +1623,7 @@
         <v>64</v>
       </c>
       <c r="N7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P7" t="str">
         <f t="shared" si="2"/>
@@ -1665,7 +1665,7 @@
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Historische und gegenwärtige Beispiele der Gruppenbildung anhand eines differenzierten Konzepts von "Meister/Jüngerschaft" erläutern können.
+Die Gruppenbildung durch die Genese, der Erhalt und die Veralltäglichung des Charismas mit historischen und gegenwärtigen Beispielen erläutern können.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -1699,7 +1699,7 @@
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Historische und gegenwärtige Beispiele der Gruppenbildung anhand eines differenzierten Konzepts von "Meister/Jüngerschaft" erläutern können.
+Die Gruppenbildung durch die Genese, der Erhalt und die Veralltäglichung des Charismas mit historischen und gegenwärtigen Beispielen erläutern können.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -1747,10 +1747,10 @@
         <v>7-Orthodoxie</v>
       </c>
       <c r="M8" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="N8" t="s">
         <v>74</v>
-      </c>
-      <c r="N8" t="s">
-        <v>75</v>
       </c>
       <c r="P8" t="str">
         <f t="shared" si="2"/>
@@ -1877,7 +1877,7 @@
         <v>65</v>
       </c>
       <c r="N9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -2004,7 +2004,7 @@
         <v>66</v>
       </c>
       <c r="N10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
@@ -2131,10 +2131,10 @@
         <v>67</v>
       </c>
       <c r="N11" t="s">
+        <v>78</v>
+      </c>
+      <c r="O11" t="s">
         <v>79</v>
-      </c>
-      <c r="O11" t="s">
-        <v>80</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -2258,13 +2258,13 @@
         <v>11-Körper</v>
       </c>
       <c r="M12" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="N12" t="s">
         <v>81</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>82</v>
-      </c>
-      <c r="O12" t="s">
-        <v>83</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
@@ -2391,10 +2391,10 @@
         <v>68</v>
       </c>
       <c r="N13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -2518,13 +2518,13 @@
         <v>13-Extremismus</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N14" t="s">
+        <v>85</v>
+      </c>
+      <c r="O14" t="s">
         <v>86</v>
-      </c>
-      <c r="O14" t="s">
-        <v>87</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -2651,7 +2651,7 @@
         <v>69</v>
       </c>
       <c r="N15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C56B14-8839-384D-B428-173CF64A7887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDF7704-BD10-3443-A19A-FB7A285D34FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -236,9 +236,6 @@
     <t>prohlMaterialeReligion2012</t>
   </si>
   <si>
-    <t>walker11Pilgrimage2018</t>
-  </si>
-  <si>
     <t>campbellContextualizingCurrentDigital2020</t>
   </si>
   <si>
@@ -348,6 +345,9 @@
   </si>
   <si>
     <t>Die Gruppenbildung durch die Genese, der Erhalt und die Veralltäglichung des Charismas mit historischen und gegenwärtigen Beispielen erläutern können.</t>
+  </si>
+  <si>
+    <t>haydenAntagonisticToleranceCompetitive2002</t>
   </si>
 </sst>
 </file>
@@ -359,9 +359,16 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -450,18 +457,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -471,20 +478,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -856,7 +864,7 @@
         <v>11</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>12</v>
@@ -865,19 +873,19 @@
         <v>13</v>
       </c>
       <c r="R1" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="S1" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="T1" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="U1" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="V1" s="14" t="s">
         <v>101</v>
-      </c>
-      <c r="V1" s="14" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -917,7 +925,7 @@
         <v>1-Vorstellung</v>
       </c>
       <c r="N2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P15" si="2">"["&amp;B2&amp;"]"</f>
@@ -1051,10 +1059,10 @@
         <v>16</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" t="s">
         <v>89</v>
-      </c>
-      <c r="G3" t="s">
-        <v>90</v>
       </c>
       <c r="I3" t="str">
         <f t="shared" ref="I3:I16" si="4">B3 &amp; ". " &amp; E3 &amp; ": " &amp; G3</f>
@@ -1065,20 +1073,20 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L16" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-Religionswissenschaft</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s">
+        <v>93</v>
+      </c>
+      <c r="O3" t="s">
         <v>94</v>
-      </c>
-      <c r="O3" t="s">
-        <v>95</v>
       </c>
       <c r="P3" t="str">
         <f t="shared" si="2"/>
@@ -1236,10 +1244,10 @@
         <v>60</v>
       </c>
       <c r="N4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1366,10 +1374,10 @@
         <v>63</v>
       </c>
       <c r="N5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1493,10 +1501,10 @@
         <v>5-Gruppen</v>
       </c>
       <c r="M6" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="N6" t="s">
         <v>103</v>
-      </c>
-      <c r="N6" t="s">
-        <v>104</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1623,7 +1631,7 @@
         <v>64</v>
       </c>
       <c r="N7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P7" t="str">
         <f t="shared" si="2"/>
@@ -1747,10 +1755,10 @@
         <v>7-Orthodoxie</v>
       </c>
       <c r="M8" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="N8" t="s">
         <v>73</v>
-      </c>
-      <c r="N8" t="s">
-        <v>74</v>
       </c>
       <c r="P8" t="str">
         <f t="shared" si="2"/>
@@ -1877,7 +1885,7 @@
         <v>65</v>
       </c>
       <c r="N9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -2004,7 +2012,7 @@
         <v>66</v>
       </c>
       <c r="N10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
@@ -2127,14 +2135,14 @@
         <f t="shared" si="5"/>
         <v>10-Orte</v>
       </c>
-      <c r="M11" s="9" t="s">
-        <v>67</v>
+      <c r="M11" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="N11" t="s">
+        <v>77</v>
+      </c>
+      <c r="O11" t="s">
         <v>78</v>
-      </c>
-      <c r="O11" t="s">
-        <v>79</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -2258,13 +2266,13 @@
         <v>11-Körper</v>
       </c>
       <c r="M12" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="N12" t="s">
         <v>80</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>81</v>
-      </c>
-      <c r="O12" t="s">
-        <v>82</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
@@ -2388,13 +2396,13 @@
         <v>12-Digitalisierung</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -2518,13 +2526,13 @@
         <v>13-Extremismus</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N14" t="s">
+        <v>84</v>
+      </c>
+      <c r="O14" t="s">
         <v>85</v>
-      </c>
-      <c r="O14" t="s">
-        <v>86</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -2648,10 +2656,10 @@
         <v>14-Interreligiös</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDF7704-BD10-3443-A19A-FB7A285D34FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79823A00-C786-1948-A437-65CD748AFACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -266,9 +266,6 @@
     <t>Erklären können, wie die Forschung an materiellen Objekten den Glauben an das Transzendente greifbar macht.</t>
   </si>
   <si>
-    <t>Erklären können, auf welche Weise Orte sakrale Bedeutung erlangen, und diese Bedeutung anhand jüdischer, christlicher und islamischer Beispiele erläutern.</t>
-  </si>
-  <si>
     <t>Was macht einen Ort für Pilger "heilig"?</t>
   </si>
   <si>
@@ -348,6 +345,9 @@
   </si>
   <si>
     <t>haydenAntagonisticToleranceCompetitive2002</t>
+  </si>
+  <si>
+    <t>Typische geographische, räumliche, rituelle und narrative Aspekte von sakralen Orten erzählen und in Verbindung mit Haydens "competitive sharing"-Modell bringen.</t>
   </si>
 </sst>
 </file>
@@ -873,19 +873,19 @@
         <v>13</v>
       </c>
       <c r="R1" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="S1" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="T1" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="U1" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="V1" s="14" t="s">
         <v>100</v>
-      </c>
-      <c r="V1" s="14" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -925,7 +925,7 @@
         <v>1-Vorstellung</v>
       </c>
       <c r="N2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P15" si="2">"["&amp;B2&amp;"]"</f>
@@ -1059,10 +1059,10 @@
         <v>16</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" t="s">
         <v>88</v>
-      </c>
-      <c r="G3" t="s">
-        <v>89</v>
       </c>
       <c r="I3" t="str">
         <f t="shared" ref="I3:I16" si="4">B3 &amp; ". " &amp; E3 &amp; ": " &amp; G3</f>
@@ -1073,20 +1073,20 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L16" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-Religionswissenschaft</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s">
+        <v>92</v>
+      </c>
+      <c r="O3" t="s">
         <v>93</v>
-      </c>
-      <c r="O3" t="s">
-        <v>94</v>
       </c>
       <c r="P3" t="str">
         <f t="shared" si="2"/>
@@ -1247,7 +1247,7 @@
         <v>69</v>
       </c>
       <c r="O4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1377,7 +1377,7 @@
         <v>70</v>
       </c>
       <c r="O5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1501,10 +1501,10 @@
         <v>5-Gruppen</v>
       </c>
       <c r="M6" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="N6" t="s">
         <v>102</v>
-      </c>
-      <c r="N6" t="s">
-        <v>103</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -2136,13 +2136,13 @@
         <v>10-Orte</v>
       </c>
       <c r="M11" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="N11" t="s">
         <v>104</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
         <v>77</v>
-      </c>
-      <c r="O11" t="s">
-        <v>78</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -2189,7 +2189,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Erklären können, auf welche Weise Orte sakrale Bedeutung erlangen, und diese Bedeutung anhand jüdischer, christlicher und islamischer Beispiele erläutern.</v>
+Typische geographische, räumliche, rituelle und narrative Aspekte von sakralen Orten erzählen und in Verbindung mit Haydens "competitive sharing"-Modell bringen.</v>
       </c>
       <c r="U11" s="15" t="str">
         <f t="shared" si="10"/>
@@ -2223,7 +2223,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-Erklären können, auf welche Weise Orte sakrale Bedeutung erlangen, und diese Bedeutung anhand jüdischer, christlicher und islamischer Beispiele erläutern.
+Typische geographische, räumliche, rituelle und narrative Aspekte von sakralen Orten erzählen und in Verbindung mit Haydens "competitive sharing"-Modell bringen.
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -2266,13 +2266,13 @@
         <v>11-Körper</v>
       </c>
       <c r="M12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="N12" t="s">
         <v>79</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>80</v>
-      </c>
-      <c r="O12" t="s">
-        <v>81</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
@@ -2314,7 +2314,7 @@
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Erklären können, auf welche Weise Orte sakrale Bedeutung erlangen, und diese Bedeutung anhand jüdischer, christlicher und islamischer Beispiele erläutern.
+Typische geographische, räumliche, rituelle und narrative Aspekte von sakralen Orten erzählen und in Verbindung mit Haydens "competitive sharing"-Modell bringen.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -2348,7 +2348,7 @@
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-Erklären können, auf welche Weise Orte sakrale Bedeutung erlangen, und diese Bedeutung anhand jüdischer, christlicher und islamischer Beispiele erläutern.
+Typische geographische, räumliche, rituelle und narrative Aspekte von sakralen Orten erzählen und in Verbindung mit Haydens "competitive sharing"-Modell bringen.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -2399,10 +2399,10 @@
         <v>67</v>
       </c>
       <c r="N13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -2526,13 +2526,13 @@
         <v>13-Extremismus</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N14" t="s">
+        <v>83</v>
+      </c>
+      <c r="O14" t="s">
         <v>84</v>
-      </c>
-      <c r="O14" t="s">
-        <v>85</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -2659,7 +2659,7 @@
         <v>68</v>
       </c>
       <c r="N15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79823A00-C786-1948-A437-65CD748AFACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62489804-0BE0-1742-AD33-40F59695CAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="102">
   <si>
     <t>blank</t>
   </si>
@@ -131,12 +131,6 @@
     <t>Extremismus</t>
   </si>
   <si>
-    <t>Interreligiös</t>
-  </si>
-  <si>
-    <t>Abschluss</t>
-  </si>
-  <si>
     <t>Was machen wir hier?</t>
   </si>
   <si>
@@ -173,12 +167,6 @@
     <t>Wie sollte religiöser Extremismus verstanden werden?</t>
   </si>
   <si>
-    <t>Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?</t>
-  </si>
-  <si>
-    <t>Wie gehe ich mit dem erworbenen Wissen um?</t>
-  </si>
-  <si>
     <t>candle.jpg</t>
   </si>
   <si>
@@ -209,9 +197,6 @@
     <t>12_iranischeSchiiten.jpeg</t>
   </si>
   <si>
-    <t>interreligious-conversation.png</t>
-  </si>
-  <si>
     <t>girl-bridge.jpg</t>
   </si>
   <si>
@@ -348,6 +333,12 @@
   </si>
   <si>
     <t>Typische geographische, räumliche, rituelle und narrative Aspekte von sakralen Orten erzählen und in Verbindung mit Haydens "competitive sharing"-Modell bringen.</t>
+  </si>
+  <si>
+    <t>Interreligiös &amp; Abschluss</t>
+  </si>
+  <si>
+    <t>Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken? / Wie gehe ich mit dem erworbenen Wissen um?</t>
   </si>
 </sst>
 </file>
@@ -800,7 +791,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -864,7 +855,7 @@
         <v>11</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>12</v>
@@ -873,19 +864,19 @@
         <v>13</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="T1" s="14" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="U1" s="14" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="V1" s="14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -896,7 +887,7 @@
         <v>45943</v>
       </c>
       <c r="D2" s="4" t="str">
-        <f t="shared" ref="D2:D16" si="0">IF(LEN(C2),TEXT(C2, "YYYY-MM-DD") &amp; "-" &amp; B2 &amp; ".md",)</f>
+        <f t="shared" ref="D2:D15" si="0">IF(LEN(C2),TEXT(C2, "YYYY-MM-DD") &amp; "-" &amp; B2 &amp; ".md",)</f>
         <v>2025-10-13-1.md</v>
       </c>
       <c r="E2" s="4" t="s">
@@ -906,7 +897,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" t="str">
@@ -914,18 +905,18 @@
         <v>1. Religion als Gegenstand: Was machen wir hier?</v>
       </c>
       <c r="J2" s="3">
-        <f t="shared" ref="J2:J16" si="1">B2</f>
+        <f t="shared" ref="J2:J15" si="1">B2</f>
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>1-Vorstellung</v>
       </c>
       <c r="N2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P15" si="2">"["&amp;B2&amp;"]"</f>
@@ -1059,13 +1050,13 @@
         <v>16</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I16" si="4">B3 &amp; ". " &amp; E3 &amp; ": " &amp; G3</f>
+        <f t="shared" ref="I3:I15" si="4">B3 &amp; ". " &amp; E3 &amp; ": " &amp; G3</f>
         <v>2. Religion als Gegenstand: Was ist die Religionswissenschaft?</v>
       </c>
       <c r="J3" s="3">
@@ -1073,27 +1064,27 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="L3" t="str">
-        <f t="shared" ref="L3:L16" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" ref="L3:L15" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-Religionswissenschaft</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="N3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="O3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="P3" t="str">
         <f t="shared" si="2"/>
         <v>[2]</v>
       </c>
       <c r="Q3" s="15" t="str">
-        <f t="shared" ref="Q3:Q16" si="6">"---
+        <f t="shared" ref="Q3:Q15" si="6">"---
 layout: post
 " &amp; B$1 &amp; ": " &amp; B3 &amp; "
 " &amp; P$1 &amp; ": " &amp; P3 &amp; "
@@ -1107,11 +1098,11 @@
 ---</v>
       </c>
       <c r="R3" s="15" t="str">
-        <f t="shared" ref="R3:R16" si="7">_xlfn.REGEXREPLACE(D3,"\.md","-slides.md")</f>
+        <f t="shared" ref="R3:R15" si="7">_xlfn.REGEXREPLACE(D3,"\.md","-slides.md")</f>
         <v>2025-10-20-2-slides.md</v>
       </c>
       <c r="S3" s="15" t="str">
-        <f t="shared" ref="S3:S16" si="8">"---
+        <f t="shared" ref="S3:S15" si="8">"---
 layout: reveal
 title: '"&amp;G3&amp;"'
 author: 'Nathan Gibson'
@@ -1135,7 +1126,7 @@
 </v>
       </c>
       <c r="T3" s="15" t="str">
-        <f t="shared" ref="T3:T16" si="9">"# Einführung in die 
+        <f t="shared" ref="T3:T15" si="9">"# Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
 ### "&amp;G3&amp;"
@@ -1163,7 +1154,7 @@
 Die Bestimmung des Fachs Religionswissenschaft in seiner Breite und mit seinen Unterschieden zur Theologie erfassen.</v>
       </c>
       <c r="U3" s="15" t="str">
-        <f t="shared" ref="U3:U16" si="10">"
+        <f t="shared" ref="U3:U14" si="10">"
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -1175,7 +1166,7 @@
 Was ist Religion?</v>
       </c>
       <c r="V3" s="15" t="str">
-        <f t="shared" ref="V3:V16" si="11">_xlfn.CONCAT(S3:U3)</f>
+        <f t="shared" ref="V3:V15" si="11">_xlfn.CONCAT(S3:U3)</f>
         <v>---
 layout: reveal
 title: 'Was ist die Religionswissenschaft?'
@@ -1223,7 +1214,7 @@
         <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I4" t="str">
         <f t="shared" si="4"/>
@@ -1234,20 +1225,20 @@
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" si="5"/>
         <v>3-Definitionen</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1353,7 +1344,7 @@
         <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I5" t="str">
         <f t="shared" si="4"/>
@@ -1364,20 +1355,20 @@
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
         <v>4-Ritual</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="N5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1483,7 +1474,7 @@
         <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I6" t="str">
         <f t="shared" si="4"/>
@@ -1494,17 +1485,17 @@
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>5-Gruppen</v>
       </c>
       <c r="M6" s="16" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="N6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1610,7 +1601,7 @@
         <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="4"/>
@@ -1621,17 +1612,17 @@
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L7" t="str">
         <f t="shared" si="5"/>
         <v>6-Gender</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="N7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="P7" t="str">
         <f t="shared" si="2"/>
@@ -1737,7 +1728,7 @@
         <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" si="4"/>
@@ -1748,17 +1739,17 @@
         <v>7</v>
       </c>
       <c r="K8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L8" t="str">
         <f t="shared" si="5"/>
         <v>7-Orthodoxie</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="N8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="P8" t="str">
         <f t="shared" si="2"/>
@@ -1864,7 +1855,7 @@
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="4"/>
@@ -1875,17 +1866,17 @@
         <v>8</v>
       </c>
       <c r="K9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
         <v>8-Schriften</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="N9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -1991,7 +1982,7 @@
         <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="4"/>
@@ -2002,17 +1993,17 @@
         <v>9</v>
       </c>
       <c r="K10" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="L10" t="str">
         <f t="shared" si="5"/>
         <v>9-Objekte</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="N10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
@@ -2118,7 +2109,7 @@
         <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
@@ -2129,20 +2120,20 @@
         <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="L11" t="str">
         <f t="shared" si="5"/>
         <v>10-Orte</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="N11" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="O11" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -2248,7 +2239,7 @@
         <v>29</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="4"/>
@@ -2259,20 +2250,20 @@
         <v>11</v>
       </c>
       <c r="K12" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="L12" t="str">
         <f t="shared" si="5"/>
         <v>11-Körper</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="N12" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="O12" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
@@ -2378,7 +2369,7 @@
         <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="4"/>
@@ -2389,20 +2380,20 @@
         <v>12</v>
       </c>
       <c r="K13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
         <v>12-Digitalisierung</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="N13" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="O13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -2495,11 +2486,11 @@
         <v>13</v>
       </c>
       <c r="C14" s="8">
-        <v>46048</v>
+        <v>46055</v>
       </c>
       <c r="D14" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>2026-01-26-13.md</v>
+        <v>2026-02-02-13.md</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>19</v>
@@ -2508,7 +2499,7 @@
         <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="4"/>
@@ -2519,20 +2510,20 @@
         <v>13</v>
       </c>
       <c r="K14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L14" t="str">
         <f t="shared" si="5"/>
         <v>13-Extremismus</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N14" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="O14" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -2549,7 +2540,7 @@
       </c>
       <c r="R14" s="15" t="str">
         <f t="shared" si="7"/>
-        <v>2026-01-26-13-slides.md</v>
+        <v>2026-02-02-13-slides.md</v>
       </c>
       <c r="S14" s="15" t="str">
         <f t="shared" si="8"/>
@@ -2587,7 +2578,7 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?</v>
+Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken? / Wie gehe ich mit dem erworbenen Wissen um?</v>
       </c>
       <c r="V14" s="15" t="str">
         <f t="shared" si="11"/>
@@ -2617,7 +2608,7 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?</v>
+Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken? / Wie gehe ich mit dem erworbenen Wissen um?</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -2625,41 +2616,41 @@
         <v>14</v>
       </c>
       <c r="C15" s="8">
-        <v>46055</v>
+        <v>46062</v>
       </c>
       <c r="D15" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>2026-02-02-14.md</v>
+        <v>2026-02-09-14.md</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" si="4"/>
-        <v>14. Religionswissenschaft für heute: Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?</v>
+        <v>14. Religionswissenschaft für heute: Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken? / Wie gehe ich mit dem erworbenen Wissen um?</v>
       </c>
       <c r="J15" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="K15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L15" t="str">
         <f t="shared" si="5"/>
-        <v>14-Interreligiös</v>
+        <v>14-Interreligiös-Abschluss</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N15" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>
@@ -2676,19 +2667,19 @@
       </c>
       <c r="R15" s="15" t="str">
         <f t="shared" si="7"/>
-        <v>2026-02-02-14-slides.md</v>
+        <v>2026-02-09-14-slides.md</v>
       </c>
       <c r="S15" s="15" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?'
+title: 'Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken? / Wie gehe ich mit dem erworbenen Wissen um?'
 author: 'Nathan Gibson'
 session: 14
 tags: [14,slides]
 category: slides
-image: interreligious-conversation.png
-parallaxBackgroundImage: 'assets/img/interreligious-conversation.png'
+image: girl-bridge.jpg
+parallaxBackgroundImage: 'assets/img/girl-bridge.jpg'
 ---
 </v>
       </c>
@@ -2697,7 +2688,7 @@
         <v># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
-### Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?
+### Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken? / Wie gehe ich mit dem erworbenen Wissen um?
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
@@ -2708,170 +2699,24 @@
 ## Heutiges Lernziel
 Überlegen und erklären können, inwieweit religionswissenschaftliche Ansätze zum interreligiösen Dialog beitragen können, sollen und dürfen.</v>
       </c>
-      <c r="U15" s="15" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">
-## Lektüre
-## Diskussion
-## Vorschau
-Wie gehe ich mit dem erworbenen Wissen um?</v>
-      </c>
-      <c r="V15" s="15" t="str">
+      <c r="U15" s="15" t="e">
+        <f>"
+## Lektüre
+## Diskussion
+## Vorschau
+"&amp;#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V15" s="15" t="e">
         <f t="shared" si="11"/>
-        <v>---
-layout: reveal
-title: 'Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?'
-author: 'Nathan Gibson'
-session: 14
-tags: [14,slides]
-category: slides
-image: interreligious-conversation.png
-parallaxBackgroundImage: 'assets/img/interreligious-conversation.png'
----
-# Einführung in die 
-### Religionswissenschaft
-{: .r-fit-text}
-### Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?
-Wintersemester 2025/2026
-Prof. Dr. Nathan Gibson
-## 📈 Rückblick: Lernziel
-Fundamentalismus, Radikalisierung und Extremismus definieren und Beispiele für jeden Begriff geben.
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-Überlegen und erklären können, inwieweit religionswissenschaftliche Ansätze zum interreligiösen Dialog beitragen können, sollen und dürfen.
-## Lektüre
-## Diskussion
-## Vorschau
-Wie gehe ich mit dem erworbenen Wissen um?</v>
+        <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="5">
-        <v>15</v>
-      </c>
-      <c r="C16" s="8">
-        <v>46062</v>
-      </c>
-      <c r="D16" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>2026-02-09-15.md</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I16" t="str">
-        <f t="shared" si="4"/>
-        <v>15. Religionswissenschaft für heute: Wie gehe ich mit dem erworbenen Wissen um?</v>
-      </c>
-      <c r="J16" s="5">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="K16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L16" t="str">
-        <f t="shared" si="5"/>
-        <v>15-Abschluss</v>
-      </c>
-      <c r="P16" t="str">
-        <f t="shared" ref="P16" si="12">"["&amp;B16&amp;"]"</f>
-        <v>[15]</v>
-      </c>
-      <c r="Q16" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>---
-layout: post
-session: 15
-tags: [15]
-level: overview
----</v>
-      </c>
-      <c r="R16" s="15" t="str">
-        <f t="shared" si="7"/>
-        <v>2026-02-09-15-slides.md</v>
-      </c>
-      <c r="S16" s="15" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">---
-layout: reveal
-title: 'Wie gehe ich mit dem erworbenen Wissen um?'
-author: 'Nathan Gibson'
-session: 15
-tags: [15,slides]
-category: slides
-image: girl-bridge.jpg
-parallaxBackgroundImage: 'assets/img/girl-bridge.jpg'
----
-</v>
-      </c>
-      <c r="T16" s="15" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve"># Einführung in die 
-### Religionswissenschaft
-{: .r-fit-text}
-### Wie gehe ich mit dem erworbenen Wissen um?
-Wintersemester 2025/2026
-Prof. Dr. Nathan Gibson
-## 📈 Rückblick: Lernziel
-Überlegen und erklären können, inwieweit religionswissenschaftliche Ansätze zum interreligiösen Dialog beitragen können, sollen und dürfen.
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-</v>
-      </c>
-      <c r="U16" s="15" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">
-## Lektüre
-## Diskussion
-## Vorschau
-</v>
-      </c>
-      <c r="V16" s="15" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">---
-layout: reveal
-title: 'Wie gehe ich mit dem erworbenen Wissen um?'
-author: 'Nathan Gibson'
-session: 15
-tags: [15,slides]
-category: slides
-image: girl-bridge.jpg
-parallaxBackgroundImage: 'assets/img/girl-bridge.jpg'
----
-# Einführung in die 
-### Religionswissenschaft
-{: .r-fit-text}
-### Wie gehe ich mit dem erworbenen Wissen um?
-Wintersemester 2025/2026
-Prof. Dr. Nathan Gibson
-## 📈 Rückblick: Lernziel
-Überlegen und erklären können, inwieweit religionswissenschaftliche Ansätze zum interreligiösen Dialog beitragen können, sollen und dürfen.
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-## Lektüre
-## Diskussion
-## Vorschau
-</v>
-      </c>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="E16" s="4"/>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E18" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
